--- a/reports/acdr2026_staff_deployment/ACDR2026_Speaking_Order_RT_TS_1006.xlsx
+++ b/reports/acdr2026_staff_deployment/ACDR2026_Speaking_Order_RT_TS_1006.xlsx
@@ -1788,6 +1788,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2010,17 +2011,17 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Cabinet Office of Japan (COJ)</t>
+          <t>Cabinet Office of Japan (COJ), with Spectee Inc. and WOTA Corp. [TBC]</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Introduction by the Cabinet Office, followed by two Japanese companies [TBC]</t>
+          <t>Introduction by the Cabinet Office (1 min), followed by Spectee Inc. and WOTA Corp. [presenters TBC]</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Companies to be confirmed</t>
+          <t>Not yet confirmed</t>
         </is>
       </c>
     </row>
@@ -2072,6 +2073,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
